--- a/VerveStacks_GHA_grids_kan10/vt_vervestacks_GHA_v1.xlsx
+++ b/VerveStacks_GHA_grids_kan10/vt_vervestacks_GHA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GHA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4C3CB19A-B2B3-450E-B69E-C8DA12BA3A18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE04435-E00E-4AA7-AF62-D8BEFB48C800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5D6D1EF9-2610-40BA-9E32-6E6936B15207}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D66325FA-4317-4486-9DB0-8B09684E28D2}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1033,7 +1033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{878CA029-4C3F-469E-B377-ACD85DDEEE7D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95D22BB-1D83-476D-B1D1-5DDA4B8432AF}">
   <dimension ref="B9:V27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2167,7 +2167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E3E8831D-5394-455A-80BF-90A7DC4FC4F9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D654B22-7FD5-43FF-A5F2-DEBDD7E5BC6E}">
   <dimension ref="B9:W40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4059,7 +4059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FFB27E6B-4BEF-4F2F-A020-CEB30F4D7DD3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5971F9-7256-405F-9F64-CBEB15DD9195}">
   <dimension ref="B9:W51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6390,7 +6390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{50D3E3B8-2774-4D60-9359-98E084EA3591}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FBB4104-1A46-400E-B93E-50EC41467E2D}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>

--- a/VerveStacks_GHA_grids_kan10/vt_vervestacks_GHA_v1.xlsx
+++ b/VerveStacks_GHA_grids_kan10/vt_vervestacks_GHA_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_GHA_grids_kan10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FBE04435-E00E-4AA7-AF62-D8BEFB48C800}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DC4983E9-DB02-4291-991A-E793E14E7D97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D66325FA-4317-4486-9DB0-8B09684E28D2}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{C9545930-3E87-4A35-B704-0D570BF15471}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -1033,7 +1033,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E95D22BB-1D83-476D-B1D1-5DDA4B8432AF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D0A65D4-3649-44CB-9873-315883BE0C94}">
   <dimension ref="B9:V27"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -2167,7 +2167,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0D654B22-7FD5-43FF-A5F2-DEBDD7E5BC6E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{867C8823-53E9-4864-801B-2CFE9EEE05DC}">
   <dimension ref="B9:W40"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -4059,7 +4059,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E5971F9-7256-405F-9F64-CBEB15DD9195}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6A20C55-EB07-4ED4-9B64-C026E61B34EB}">
   <dimension ref="B9:W51"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -6390,7 +6390,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6FBB4104-1A46-400E-B93E-50EC41467E2D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8658391D-9917-44FB-8C0E-4E8ACA290D56}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
